--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -2472,8 +2472,15 @@
         <v>45522.64583333334</v>
       </c>
       <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Stadio Nicola Ceravolo
+ (Catanzaro)</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>14650</v>
+      </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,46 +512,46 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45529.5625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sacchi J. L.
+          <t>Sozza S.
  (Ita)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stadio Ennio Tardini
- (Parma)</t>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>27906</v>
+        <v>43147</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,202 +580,968 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45529.5625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Doveri D.
+          <t>Rapuano A.
  (Ita)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico di Torino
+ (Turin)</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>28177</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>77</v>
+      </c>
+      <c r="L3" t="n">
+        <v>771</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>UilLdutJ</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45529.65625</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Zufferli L.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>77</v>
+      </c>
+      <c r="L4" t="n">
+        <v>771</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>2uc40Ntf</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45529.65625</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Pairetto L.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Stadio Diego Armando Maradona
+ (Naples)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>54726</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>77</v>
+      </c>
+      <c r="L5" t="n">
+        <v>771</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>0hYMmpcl</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45530.5625</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Di Bello M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Unipol Domus
+ (Cagliari)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>16416</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>77</v>
+      </c>
+      <c r="L6" t="n">
+        <v>771</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>fZZxp2dD</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45530.65625</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Giua A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Stadio Marc'Antonio Bentegodi
+ (Verona)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>39211</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>77</v>
+      </c>
+      <c r="L7" t="n">
+        <v>771</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>EaryFQkA</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45534.5625</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Stadio Pierluigi Penzo
+ (Venice)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>11150</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>77</v>
+      </c>
+      <c r="L8" t="n">
+        <v>771</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>WdSjHeFt</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45534.65625</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>77</v>
+      </c>
+      <c r="L9" t="n">
+        <v>771</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>ELeQ0zVa</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45535.5625</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stadio Renato Dall'Ara
+ (Bologna)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>38279</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>77</v>
+      </c>
+      <c r="L10" t="n">
+        <v>771</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>d4DGBiqI</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45535.5625</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stadio Via del Mare
+ (Lecce)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>40670</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>77</v>
+      </c>
+      <c r="L11" t="n">
+        <v>771</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>0xK7DDE5</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45535.65625</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>77</v>
+      </c>
+      <c r="L12" t="n">
+        <v>771</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SjzlgqTj</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45535.65625</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Stadio Diego Armando Maradona
+ (Naples)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>54726</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>77</v>
+      </c>
+      <c r="L13" t="n">
+        <v>771</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>nZgYbEaC</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45536.5625</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>43147</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>77</v>
+      </c>
+      <c r="L14" t="n">
+        <v>771</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>r1mschUO</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45536.5625</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>77</v>
+      </c>
+      <c r="L15" t="n">
+        <v>771</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>hCGaFZqg</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45536.65625</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Allianz Stadium
+ (Turin)</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>41507</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>77</v>
+      </c>
+      <c r="L16" t="n">
+        <v>771</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>6ZvTGnLc</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45536.65625</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
         <is>
           <t>Bluenergy Stadium - Stadio Friuli
  (Udine)</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E17" t="n">
         <v>25144</v>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
         <is>
           <t>rXw8YKDE</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Udinese</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>URcSl02h</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Lazio</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
         <v>77</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L17" t="n">
         <v>771</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M17" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N17" t="n">
         <v>20242025</v>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>AsIP75lK</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45528.65625</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Di Marco D.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Stadio Giuseppe Meazza (San Siro)
- (Milan)</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>80018</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Inter</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>G8lYsMgU</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Lecce</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>77</v>
-      </c>
-      <c r="L4" t="n">
-        <v>771</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>6D3e2qCs</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45528.65625</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Mariani M.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Brianteo
- (Monza)</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>17102</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>4YSMlwj7</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Monza</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>d0PJxeie</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Genoa</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>77</v>
-      </c>
-      <c r="L5" t="n">
-        <v>771</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>Serie A</t>
         </is>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,46 +512,46 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>M7MVoOR0</t>
+          <t>0hYMmpcl</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45529.5625</v>
+        <v>45530.5625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sozza S.
+          <t>Di Bello M.
  (Ita)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stadio Artemio Franchi
- (Florence)</t>
+          <t>Unipol Domus
+ (Cagliari)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>43147</v>
+        <v>16416</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,46 +580,46 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>dbt7KrYP</t>
+          <t>fZZxp2dD</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45529.5625</v>
+        <v>45530.65625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rapuano A.
+          <t>Giua A.
  (Ita)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stadio Olimpico di Torino
- (Turin)</t>
+          <t>Stadio Marc'Antonio Bentegodi
+ (Verona)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>28177</v>
+        <v>39211</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -648,46 +648,41 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>UilLdutJ</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45529.65625</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Zufferli L.
- (Ita)</t>
-        </is>
-      </c>
+        <v>45534.5625</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stadio Olimpico
- (Rome)</t>
+          <t>Stadio Pierluigi Penzo
+ (Venice)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>70634</v>
+        <v>11150</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>AS Roma</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>MZFZnvX4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -716,46 +711,41 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2uc40Ntf</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45529.65625</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Pairetto L.
- (Ita)</t>
-        </is>
-      </c>
+        <v>45534.65625</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stadio Diego Armando Maradona
- (Naples)</t>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>54726</v>
+        <v>80018</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -784,46 +774,41 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0hYMmpcl</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45530.5625</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Di Bello M.
- (Ita)</t>
-        </is>
-      </c>
+        <v>45535.5625</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Unipol Domus
- (Cagliari)</t>
+          <t>Stadio Renato Dall'Ara
+ (Bologna)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>16416</v>
+        <v>38279</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -852,46 +837,41 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>fZZxp2dD</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45530.65625</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Giua A.
- (Ita)</t>
-        </is>
-      </c>
+        <v>45535.5625</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Stadio Marc'Antonio Bentegodi
- (Verona)</t>
+          <t>Stadio Via del Mare
+ (Lecce)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>39211</v>
+        <v>40670</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -920,41 +900,41 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EaryFQkA</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45534.5625</v>
+        <v>45535.65625</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stadio Pierluigi Penzo
- (Venice)</t>
+          <t>Stadio Olimpico
+ (Rome)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>11150</v>
+        <v>70634</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -983,41 +963,41 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>WdSjHeFt</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45534.65625</v>
+        <v>45535.65625</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stadio Giuseppe Meazza (San Siro)
- (Milan)</t>
+          <t>Stadio Diego Armando Maradona
+ (Naples)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>80018</v>
+        <v>54726</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1046,41 +1026,41 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45536.5625</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Stadio Renato Dall'Ara
- (Bologna)</t>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>38279</v>
+        <v>43147</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1109,41 +1089,41 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45536.5625</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Stadio Via del Mare
- (Lecce)</t>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>40670</v>
+        <v>36599</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1172,41 +1152,41 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45535.65625</v>
+        <v>45536.65625</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Stadio Olimpico
- (Rome)</t>
+          <t>Allianz Stadium
+ (Turin)</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>70634</v>
+        <v>41507</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>AS Roma</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1235,41 +1215,41 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45535.65625</v>
+        <v>45536.65625</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Stadio Diego Armando Maradona
- (Naples)</t>
+          <t>Bluenergy Stadium - Stadio Friuli
+ (Udine)</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>54726</v>
+        <v>25144</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1290,258 +1270,6 @@
         </is>
       </c>
       <c r="P13" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>nZgYbEaC</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45536.5625</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Stadio Artemio Franchi
- (Florence)</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>43147</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Fiorentina</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>4YSMlwj7</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Monza</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>77</v>
-      </c>
-      <c r="L14" t="n">
-        <v>771</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>r1mschUO</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45536.5625</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Stadio Luigi Ferraris
- (Genoa)</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>36599</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>d0PJxeie</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Genoa</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>rJVAIaHo</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Verona</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>77</v>
-      </c>
-      <c r="L15" t="n">
-        <v>771</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Allianz Stadium
- (Turin)</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>41507</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Juventus</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>zVqqL0ma</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>AS Roma</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>77</v>
-      </c>
-      <c r="L16" t="n">
-        <v>771</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Bluenergy Stadium - Stadio Friuli
- (Udine)</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>25144</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>rXw8YKDE</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Udinese</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Como</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>77</v>
-      </c>
-      <c r="L17" t="n">
-        <v>771</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
         <is>
           <t>Serie A</t>
         </is>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,46 +512,41 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0hYMmpcl</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45530.5625</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Di Bello M.
- (Ita)</t>
-        </is>
-      </c>
+        <v>45534.5625</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Unipol Domus
- (Cagliari)</t>
+          <t>Stadio Pierluigi Penzo
+ (Venice)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>16416</v>
+        <v>11150</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>MZFZnvX4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,46 +575,41 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fZZxp2dD</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45530.65625</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Giua A.
- (Ita)</t>
-        </is>
-      </c>
+        <v>45534.65625</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stadio Marc'Antonio Bentegodi
- (Verona)</t>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>39211</v>
+        <v>80018</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -648,41 +638,41 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>EaryFQkA</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45534.5625</v>
+        <v>45535.5625</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stadio Pierluigi Penzo
- (Venice)</t>
+          <t>Stadio Renato Dall'Ara
+ (Bologna)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>11150</v>
+        <v>38279</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -711,41 +701,41 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WdSjHeFt</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45534.65625</v>
+        <v>45535.5625</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stadio Giuseppe Meazza (San Siro)
- (Milan)</t>
+          <t>Stadio Via del Mare
+ (Lecce)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>80018</v>
+        <v>40670</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -774,41 +764,41 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45535.65625</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stadio Renato Dall'Ara
- (Bologna)</t>
+          <t>Stadio Olimpico
+ (Rome)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>38279</v>
+        <v>70634</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -837,41 +827,41 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45535.65625</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Stadio Via del Mare
- (Lecce)</t>
+          <t>Stadio Diego Armando Maradona
+ (Naples)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>40670</v>
+        <v>54726</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -900,41 +890,41 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45535.65625</v>
+        <v>45536.5625</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stadio Olimpico
- (Rome)</t>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>70634</v>
+        <v>43147</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -963,41 +953,41 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45535.65625</v>
+        <v>45536.5625</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stadio Diego Armando Maradona
- (Naples)</t>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>54726</v>
+        <v>36599</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1026,41 +1016,41 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>nZgYbEaC</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45536.5625</v>
+        <v>45536.65625</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Stadio Artemio Franchi
- (Florence)</t>
+          <t>Allianz Stadium
+ (Turin)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>43147</v>
+        <v>41507</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>AS Roma</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1089,41 +1079,41 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>r1mschUO</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45536.5625</v>
+        <v>45536.65625</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Stadio Luigi Ferraris
- (Genoa)</t>
+          <t>Bluenergy Stadium - Stadio Friuli
+ (Udine)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>36599</v>
+        <v>25144</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1144,132 +1134,6 @@
         </is>
       </c>
       <c r="P11" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Allianz Stadium
- (Turin)</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>41507</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Juventus</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>zVqqL0ma</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>AS Roma</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>77</v>
-      </c>
-      <c r="L12" t="n">
-        <v>771</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Bluenergy Stadium - Stadio Friuli
- (Udine)</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>25144</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>rXw8YKDE</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Udinese</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Como</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>77</v>
-      </c>
-      <c r="L13" t="n">
-        <v>771</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
         <is>
           <t>Serie A</t>
         </is>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,41 +512,46 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>EaryFQkA</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45534.5625</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>45535.5625</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Marinelli L.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stadio Pierluigi Penzo
- (Venice)</t>
+          <t>Stadio Renato Dall'Ara
+ (Bologna)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>11150</v>
+        <v>38279</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -575,41 +580,46 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WdSjHeFt</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45534.65625</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>45535.5625</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Fabbri M.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stadio Giuseppe Meazza (San Siro)
- (Milan)</t>
+          <t>Stadio Via del Mare
+ (Lecce)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>80018</v>
+        <v>40670</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -638,41 +648,46 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45535.5625</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>45535.65625</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Massa D.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stadio Renato Dall'Ara
- (Bologna)</t>
+          <t>Stadio Olimpico
+ (Rome)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>38279</v>
+        <v>70634</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -701,41 +716,46 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45535.5625</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>45535.65625</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Tremolada P.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stadio Via del Mare
- (Lecce)</t>
+          <t>Stadio Diego Armando Maradona
+ (Naples)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>40670</v>
+        <v>54726</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -764,41 +784,46 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45535.65625</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>45536.5625</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Colombo A.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stadio Olimpico
- (Rome)</t>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>70634</v>
+        <v>43147</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -827,41 +852,46 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45535.65625</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>45536.5625</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ayroldi G.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Stadio Diego Armando Maradona
- (Naples)</t>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>54726</v>
+        <v>36599</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -890,41 +920,46 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nZgYbEaC</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45536.5625</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+        <v>45536.65625</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Guida M.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stadio Artemio Franchi
- (Florence)</t>
+          <t>Allianz Stadium
+ (Turin)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>43147</v>
+        <v>41507</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>AS Roma</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -953,41 +988,46 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>r1mschUO</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45536.5625</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>45536.65625</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Prontera A.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stadio Luigi Ferraris
- (Genoa)</t>
+          <t>Bluenergy Stadium - Stadio Friuli
+ (Udine)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>36599</v>
+        <v>25144</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1008,132 +1048,6 @@
         </is>
       </c>
       <c r="P9" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Allianz Stadium
- (Turin)</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>41507</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Juventus</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>zVqqL0ma</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>AS Roma</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>77</v>
-      </c>
-      <c r="L10" t="n">
-        <v>771</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Bluenergy Stadium - Stadio Friuli
- (Udine)</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>25144</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>rXw8YKDE</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Udinese</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Como</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>77</v>
-      </c>
-      <c r="L11" t="n">
-        <v>771</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
         <is>
           <t>Serie A</t>
         </is>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,46 +512,46 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45536.5625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Marinelli L.
+          <t>Colombo A.
  (Ita)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stadio Renato Dall'Ara
- (Bologna)</t>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>38279</v>
+        <v>43147</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,46 +580,46 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45536.5625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fabbri M.
+          <t>Ayroldi G.
  (Ita)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stadio Via del Mare
- (Lecce)</t>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>40670</v>
+        <v>36599</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -648,46 +648,46 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45535.65625</v>
+        <v>45536.65625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Massa D.
+          <t>Guida M.
  (Ita)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stadio Olimpico
- (Rome)</t>
+          <t>Allianz Stadium
+ (Turin)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>70634</v>
+        <v>41507</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>AS Roma</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -716,46 +716,46 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45535.65625</v>
+        <v>45536.65625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tremolada P.
+          <t>Prontera A.
  (Ita)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stadio Diego Armando Maradona
- (Naples)</t>
+          <t>Bluenergy Stadium - Stadio Friuli
+ (Udine)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>54726</v>
+        <v>25144</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -776,278 +776,6 @@
         </is>
       </c>
       <c r="P5" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>nZgYbEaC</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45536.5625</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Colombo A.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Stadio Artemio Franchi
- (Florence)</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>43147</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Fiorentina</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4YSMlwj7</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Monza</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>77</v>
-      </c>
-      <c r="L6" t="n">
-        <v>771</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>r1mschUO</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45536.5625</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ayroldi G.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Stadio Luigi Ferraris
- (Genoa)</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>36599</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>d0PJxeie</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Genoa</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>rJVAIaHo</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Verona</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>77</v>
-      </c>
-      <c r="L7" t="n">
-        <v>771</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Guida M.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Allianz Stadium
- (Turin)</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>41507</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Juventus</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>zVqqL0ma</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>AS Roma</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>77</v>
-      </c>
-      <c r="L8" t="n">
-        <v>771</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Prontera A.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Bluenergy Stadium - Stadio Friuli
- (Udine)</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>25144</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>rXw8YKDE</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Udinese</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Como</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>77</v>
-      </c>
-      <c r="L9" t="n">
-        <v>771</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
         <is>
           <t>Serie A</t>
         </is>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,46 +512,41 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>nZgYbEaC</t>
+          <t>n7VN5MCd</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45536.5625</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Colombo A.
- (Ita)</t>
-        </is>
-      </c>
+        <v>45549.41666666666</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stadio Artemio Franchi
- (Florence)</t>
+          <t>Stadio Giuseppe Sinigaglia
+ (Como)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>43147</v>
+        <v>13602</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,46 +575,41 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>r1mschUO</t>
+          <t>v1I9TP43</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45536.5625</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ayroldi G.
- (Ita)</t>
-        </is>
-      </c>
+        <v>45549.54166666666</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stadio Luigi Ferraris
- (Genoa)</t>
+          <t>Stadio Carlo Castellani
+ (Empoli)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>36599</v>
+        <v>16284</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -648,46 +638,41 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hCGaFZqg</t>
+          <t>SQjcKLRk</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Guida M.
- (Ita)</t>
-        </is>
-      </c>
+        <v>45549.65625</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Allianz Stadium
- (Turin)</t>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>41507</v>
+        <v>80018</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>AS Roma</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -716,46 +701,41 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6ZvTGnLc</t>
+          <t>zTBIR3ZF</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Prontera A.
- (Ita)</t>
-        </is>
-      </c>
+        <v>45550.3125</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bluenergy Stadium - Stadio Friuli
- (Udine)</t>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>25144</v>
+        <v>36599</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>AS Roma</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -776,6 +756,384 @@
         </is>
       </c>
       <c r="P5" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>zFWqD4KM</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45550.41666666666</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Gewiss Stadium
+ (Bergamo)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>21747</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>77</v>
+      </c>
+      <c r="L6" t="n">
+        <v>771</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>4WHcOkpL</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45550.41666666666</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico di Torino
+ (Turin)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>28177</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>77</v>
+      </c>
+      <c r="L7" t="n">
+        <v>771</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>6cNF7rrp</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45550.54166666666</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Unipol Domus
+ (Cagliari)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>16416</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>77</v>
+      </c>
+      <c r="L8" t="n">
+        <v>771</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Esk5Iad2</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45550.65625</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Brianteo
+ (Monza)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>17102</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>77</v>
+      </c>
+      <c r="L9" t="n">
+        <v>771</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>WIJkQBF8</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45551.5625</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stadio Ennio Tardini
+ (Parma)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>27906</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>77</v>
+      </c>
+      <c r="L10" t="n">
+        <v>771</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>rgFQPs4S</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45551.65625</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>77</v>
+      </c>
+      <c r="L11" t="n">
+        <v>771</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>Serie A</t>
         </is>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1139,6 +1139,636 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2ucWYubt</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45555.5625</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Unipol Domus
+ (Cagliari)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>16416</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>77</v>
+      </c>
+      <c r="L12" t="n">
+        <v>771</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>44gmVcc5</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45555.65625</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Stadio Marc'Antonio Bentegodi
+ (Verona)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>39211</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>77</v>
+      </c>
+      <c r="L13" t="n">
+        <v>771</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>S66wtFBN</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45556.41666666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Stadio Pierluigi Penzo
+ (Venice)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>11150</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>77</v>
+      </c>
+      <c r="L14" t="n">
+        <v>771</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Yqo4RFdU</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45556.54166666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Allianz Stadium
+ (Turin)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>41507</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>77</v>
+      </c>
+      <c r="L15" t="n">
+        <v>771</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>O8QDoJsn</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45556.65625</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Stadio Via del Mare
+ (Lecce)</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>40670</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>77</v>
+      </c>
+      <c r="L16" t="n">
+        <v>771</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>A50vXJSh</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45557.3125</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>43147</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>77</v>
+      </c>
+      <c r="L17" t="n">
+        <v>771</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>pOEMqcCb</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45557.41666666666</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Brianteo
+ (Monza)</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>17102</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>77</v>
+      </c>
+      <c r="L18" t="n">
+        <v>771</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>WvDUsysB</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45557.54166666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>77</v>
+      </c>
+      <c r="L19" t="n">
+        <v>771</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>xIieTySH</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45557.65625</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>77</v>
+      </c>
+      <c r="L20" t="n">
+        <v>771</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>OAeKROjD</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45558.65625</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Gewiss Stadium
+ (Bergamo)</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>21747</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>77</v>
+      </c>
+      <c r="L21" t="n">
+        <v>771</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,474 +512,1258 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zTBIR3ZF</t>
+          <t>2ucWYubt</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.3125</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Giua A.
- (Ita)</t>
-        </is>
-      </c>
+        <v>45555.5625</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>Unipol Domus
+ (Cagliari)</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>16416</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>77</v>
+      </c>
+      <c r="L2" t="n">
+        <v>771</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>44gmVcc5</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45555.65625</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Stadio Marc'Antonio Bentegodi
+ (Verona)</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>39211</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>77</v>
+      </c>
+      <c r="L3" t="n">
+        <v>771</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>S66wtFBN</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45556.41666666666</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Stadio Pierluigi Penzo
+ (Venice)</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>11150</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>77</v>
+      </c>
+      <c r="L4" t="n">
+        <v>771</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Yqo4RFdU</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45556.54166666666</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Allianz Stadium
+ (Turin)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>41507</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>77</v>
+      </c>
+      <c r="L5" t="n">
+        <v>771</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>O8QDoJsn</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45556.65625</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Stadio Via del Mare
+ (Lecce)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>40670</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>77</v>
+      </c>
+      <c r="L6" t="n">
+        <v>771</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>A50vXJSh</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45557.3125</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>43147</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>77</v>
+      </c>
+      <c r="L7" t="n">
+        <v>771</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>pOEMqcCb</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45557.41666666666</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Brianteo
+ (Monza)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>17102</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>77</v>
+      </c>
+      <c r="L8" t="n">
+        <v>771</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>WvDUsysB</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45557.54166666666</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>77</v>
+      </c>
+      <c r="L9" t="n">
+        <v>771</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>xIieTySH</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45557.65625</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>77</v>
+      </c>
+      <c r="L10" t="n">
+        <v>771</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>OAeKROjD</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45558.65625</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Gewiss Stadium
+ (Bergamo)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>24950</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>77</v>
+      </c>
+      <c r="L11" t="n">
+        <v>771</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CCDxBZAc</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45562.65625</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>77</v>
+      </c>
+      <c r="L12" t="n">
+        <v>771</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>pIgDNCf3</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45563.41666666666</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Bluenergy Stadium - Stadio Friuli
+ (Udine)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>25144</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>77</v>
+      </c>
+      <c r="L13" t="n">
+        <v>771</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>KIQjmWIj</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45563.54166666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
         <is>
           <t>Stadio Luigi Ferraris
  (Genoa)</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E14" t="n">
         <v>36599</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
         <is>
           <t>d0PJxeie</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Genoa</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>zVqqL0ma</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>AS Roma</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>77</v>
-      </c>
-      <c r="L2" t="n">
-        <v>771</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>zFWqD4KM</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>45550.41666666666</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Sacchi J. L.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Gewiss Stadium
- (Bergamo)</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>21747</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>77</v>
+      </c>
+      <c r="L14" t="n">
+        <v>771</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Whh3dzd4</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45563.65625</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Stadio Renato Dall'Ara
+ (Bologna)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>38279</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>8C9JjMXu</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Atalanta</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Fiorentina</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>77</v>
-      </c>
-      <c r="L3" t="n">
-        <v>771</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>4WHcOkpL</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45550.41666666666</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Colombo A.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="K15" t="n">
+        <v>77</v>
+      </c>
+      <c r="L15" t="n">
+        <v>771</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>WxCQa92d</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45564.3125</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Stadio Olimpico di Torino
  (Turin)</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E16" t="n">
         <v>28177</v>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
         <is>
           <t>MZFZnvX4</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Torino</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>G8lYsMgU</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Lecce</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>77</v>
-      </c>
-      <c r="L4" t="n">
-        <v>771</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>6cNF7rrp</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45550.54166666666</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>La Penna F.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Unipol Domus
- (Cagliari)</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>16416</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SCGVmKHb</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>77</v>
+      </c>
+      <c r="L16" t="n">
+        <v>771</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>OC8I1VXq</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>77</v>
+      </c>
+      <c r="L17" t="n">
+        <v>771</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>h8tCfEQG</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Sinigaglia
+ (Como)</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>13602</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>77</v>
+      </c>
+      <c r="L18" t="n">
+        <v>771</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>0YqKhheT</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45564.54166666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Stadio Carlo Castellani
+ (Empoli)</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>16284</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>77</v>
+      </c>
+      <c r="L19" t="n">
+        <v>771</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>WETw9DuA</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45564.65625</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Stadio Diego Armando Maradona
+ (Naples)</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>54726</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
         <is>
           <t>69Dxbc61</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Napoli</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>77</v>
-      </c>
-      <c r="L5" t="n">
-        <v>771</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Esk5Iad2</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45550.65625</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Pairetto L.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Brianteo
- (Monza)</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>17102</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>4YSMlwj7</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Monza</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Inter</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>77</v>
-      </c>
-      <c r="L6" t="n">
-        <v>771</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>WIJkQBF8</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45551.5625</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Abisso R.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="K20" t="n">
+        <v>77</v>
+      </c>
+      <c r="L20" t="n">
+        <v>771</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vuXo7iAM</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45565.65625</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
         <is>
           <t>Stadio Ennio Tardini
  (Parma)</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E21" t="n">
         <v>27906</v>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
         <is>
           <t>6DxlaxHN</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Parma</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>rXw8YKDE</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Udinese</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>77</v>
-      </c>
-      <c r="L7" t="n">
-        <v>771</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>rgFQPs4S</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45551.65625</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Zufferli L.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Stadio Olimpico
- (Rome)</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>70634</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>URcSl02h</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Lazio</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>rJVAIaHo</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Verona</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>77</v>
-      </c>
-      <c r="L8" t="n">
-        <v>771</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>77</v>
+      </c>
+      <c r="L21" t="n">
+        <v>771</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
         <is>
           <t>Serie A</t>
         </is>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,41 +512,46 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2ucWYubt</t>
+          <t>S66wtFBN</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45555.5625</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>45556.41666666666</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Marchetti M.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Unipol Domus
- (Cagliari)</t>
+          <t>Stadio Pierluigi Penzo
+ (Venice)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>16416</v>
+        <v>11150</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -575,41 +580,46 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>44gmVcc5</t>
+          <t>Yqo4RFdU</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45555.65625</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>45556.54166666666</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Doveri D.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stadio Marc'Antonio Bentegodi
- (Verona)</t>
+          <t>Allianz Stadium
+ (Turin)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>39211</v>
+        <v>41507</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -638,41 +648,46 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>S66wtFBN</t>
+          <t>O8QDoJsn</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45556.41666666666</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>45556.65625</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Guida M.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stadio Pierluigi Penzo
- (Venice)</t>
+          <t>Stadio Via del Mare
+ (Lecce)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>11150</v>
+        <v>40670</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -701,41 +716,46 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Yqo4RFdU</t>
+          <t>A50vXJSh</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45556.54166666666</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>45557.3125</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Marcenaro M.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Allianz Stadium
- (Turin)</t>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>41507</v>
+        <v>43147</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -764,41 +784,46 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>O8QDoJsn</t>
+          <t>pOEMqcCb</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45556.65625</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>45557.41666666666</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Massa D.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stadio Via del Mare
- (Lecce)</t>
+          <t>Brianteo
+ (Monza)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>40670</v>
+        <v>17102</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -827,41 +852,46 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>A50vXJSh</t>
+          <t>WvDUsysB</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45557.3125</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>45557.54166666666</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Feliciani E.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Stadio Artemio Franchi
- (Florence)</t>
+          <t>Stadio Olimpico
+ (Rome)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>43147</v>
+        <v>70634</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>AS Roma</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -890,41 +920,46 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>pOEMqcCb</t>
+          <t>xIieTySH</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45557.41666666666</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+        <v>45557.65625</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Mariani M.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Brianteo
- (Monza)</t>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>17102</v>
+        <v>80018</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -953,41 +988,46 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>WvDUsysB</t>
+          <t>OAeKROjD</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45557.54166666666</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>45558.65625</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Tremolada P.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stadio Olimpico
- (Rome)</t>
+          <t>Gewiss Stadium
+ (Bergamo)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>70634</v>
+        <v>24950</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>AS Roma</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1008,762 +1048,6 @@
         </is>
       </c>
       <c r="P9" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>xIieTySH</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45557.65625</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Stadio Giuseppe Meazza (San Siro)
- (Milan)</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>80018</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Inter</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>8Sa8HInO</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>AC Milan</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>77</v>
-      </c>
-      <c r="L10" t="n">
-        <v>771</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>OAeKROjD</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45558.65625</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Gewiss Stadium
- (Bergamo)</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>24950</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>8C9JjMXu</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Atalanta</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Como</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>77</v>
-      </c>
-      <c r="L11" t="n">
-        <v>771</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>CCDxBZAc</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45562.65625</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Stadio Giuseppe Meazza (San Siro)
- (Milan)</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>80018</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>8Sa8HInO</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>AC Milan</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>G8lYsMgU</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Lecce</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>77</v>
-      </c>
-      <c r="L12" t="n">
-        <v>771</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>pIgDNCf3</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45563.41666666666</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Bluenergy Stadium - Stadio Friuli
- (Udine)</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>25144</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>rXw8YKDE</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Udinese</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Inter</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>77</v>
-      </c>
-      <c r="L13" t="n">
-        <v>771</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>KIQjmWIj</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45563.54166666666</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Stadio Luigi Ferraris
- (Genoa)</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>36599</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>d0PJxeie</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Genoa</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Juventus</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>77</v>
-      </c>
-      <c r="L14" t="n">
-        <v>771</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Whh3dzd4</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45563.65625</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Stadio Renato Dall'Ara
- (Bologna)</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>38279</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0M9xNN8N</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Bologna</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>8C9JjMXu</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Atalanta</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>77</v>
-      </c>
-      <c r="L15" t="n">
-        <v>771</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>WxCQa92d</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45564.3125</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Stadio Olimpico di Torino
- (Turin)</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>28177</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>MZFZnvX4</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Torino</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>URcSl02h</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Lazio</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>77</v>
-      </c>
-      <c r="L16" t="n">
-        <v>771</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>OC8I1VXq</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45564.41666666666</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Stadio Olimpico
- (Rome)</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>70634</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>zVqqL0ma</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>AS Roma</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>MkPmVv50</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Venezia</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>77</v>
-      </c>
-      <c r="L17" t="n">
-        <v>771</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>h8tCfEQG</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45564.41666666666</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Stadio Giuseppe Sinigaglia
- (Como)</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>13602</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Como</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>rJVAIaHo</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Verona</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>77</v>
-      </c>
-      <c r="L18" t="n">
-        <v>771</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>0YqKhheT</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45564.54166666666</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Stadio Carlo Castellani
- (Empoli)</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>16284</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0ESCnI1H</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Empoli</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Fiorentina</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>77</v>
-      </c>
-      <c r="L19" t="n">
-        <v>771</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>WETw9DuA</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45564.65625</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Stadio Diego Armando Maradona
- (Naples)</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>54726</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Napoli</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>4YSMlwj7</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Monza</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>77</v>
-      </c>
-      <c r="L20" t="n">
-        <v>771</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>vuXo7iAM</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45565.65625</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Stadio Ennio Tardini
- (Parma)</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>27906</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>6DxlaxHN</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>SCGVmKHb</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>77</v>
-      </c>
-      <c r="L21" t="n">
-        <v>771</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
         <is>
           <t>Serie A</t>
         </is>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,474 +512,1326 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zTBIR3ZF</t>
+          <t>OAeKROjD</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.3125</v>
+        <v>45558.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Giua A.
+          <t>Tremolada P.
  (Ita)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>Gewiss Stadium
+ (Bergamo)</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>24950</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>77</v>
+      </c>
+      <c r="L2" t="n">
+        <v>771</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>CCDxBZAc</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45562.65625</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>77</v>
+      </c>
+      <c r="L3" t="n">
+        <v>771</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>pIgDNCf3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45563.41666666666</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Bluenergy Stadium - Stadio Friuli
+ (Udine)</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>25144</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>77</v>
+      </c>
+      <c r="L4" t="n">
+        <v>771</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>KIQjmWIj</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45563.54166666666</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
         <is>
           <t>Stadio Luigi Ferraris
  (Genoa)</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E5" t="n">
         <v>36599</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
         <is>
           <t>d0PJxeie</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Genoa</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>77</v>
+      </c>
+      <c r="L5" t="n">
+        <v>771</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Whh3dzd4</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45563.65625</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Stadio Renato Dall'Ara
+ (Bologna)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>38279</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>77</v>
+      </c>
+      <c r="L6" t="n">
+        <v>771</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>WxCQa92d</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45564.3125</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico di Torino
+ (Turin)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>28177</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>77</v>
+      </c>
+      <c r="L7" t="n">
+        <v>771</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>OC8I1VXq</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
         <is>
           <t>zVqqL0ma</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>AS Roma</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>77</v>
-      </c>
-      <c r="L2" t="n">
-        <v>771</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>zFWqD4KM</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>45550.41666666666</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Sacchi J. L.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>77</v>
+      </c>
+      <c r="L8" t="n">
+        <v>771</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>h8tCfEQG</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Sinigaglia
+ (Como)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>13602</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>77</v>
+      </c>
+      <c r="L9" t="n">
+        <v>771</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>0YqKhheT</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45564.54166666666</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stadio Carlo Castellani
+ (Empoli)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>16284</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>77</v>
+      </c>
+      <c r="L10" t="n">
+        <v>771</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>WETw9DuA</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45564.65625</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stadio Diego Armando Maradona
+ (Naples)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>54726</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>77</v>
+      </c>
+      <c r="L11" t="n">
+        <v>771</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>vuXo7iAM</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45565.65625</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Stadio Ennio Tardini
+ (Parma)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>27906</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>77</v>
+      </c>
+      <c r="L12" t="n">
+        <v>771</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>z3jsi9f5</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45569.5625</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Stadio Diego Armando Maradona
+ (Naples)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>54726</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>77</v>
+      </c>
+      <c r="L13" t="n">
+        <v>771</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>8SWavWAa</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45569.65625</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Stadio Marc'Antonio Bentegodi
+ (Verona)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>39211</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>77</v>
+      </c>
+      <c r="L14" t="n">
+        <v>771</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WUqjkmPH</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45570.41666666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Bluenergy Stadium - Stadio Friuli
+ (Udine)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>25144</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>77</v>
+      </c>
+      <c r="L15" t="n">
+        <v>771</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>EB8yv2aJ</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45570.54166666666</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Gewiss Stadium
  (Bergamo)</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>21747</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="E16" t="n">
+        <v>24950</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
         <is>
           <t>8C9JjMXu</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Atalanta</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Fiorentina</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>77</v>
-      </c>
-      <c r="L3" t="n">
-        <v>771</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>4WHcOkpL</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45550.41666666666</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Colombo A.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Stadio Olimpico di Torino
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>77</v>
+      </c>
+      <c r="L16" t="n">
+        <v>771</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>ttV7xAuC</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45570.65625</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>77</v>
+      </c>
+      <c r="L17" t="n">
+        <v>771</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>x8OGzlAO</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45571.3125</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Allianz Stadium
  (Turin)</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>28177</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>MZFZnvX4</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Torino</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>G8lYsMgU</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Lecce</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>77</v>
-      </c>
-      <c r="L4" t="n">
-        <v>771</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>6cNF7rrp</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45550.54166666666</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>La Penna F.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Unipol Domus
- (Cagliari)</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>16416</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+      <c r="E18" t="n">
+        <v>41507</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>SCGVmKHb</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Cagliari</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Napoli</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>77</v>
-      </c>
-      <c r="L5" t="n">
-        <v>771</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Esk5Iad2</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45550.65625</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Pairetto L.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="K18" t="n">
+        <v>77</v>
+      </c>
+      <c r="L18" t="n">
+        <v>771</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>dzYLoEIP</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Stadio Renato Dall'Ara
+ (Bologna)</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>38279</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>77</v>
+      </c>
+      <c r="L19" t="n">
+        <v>771</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>SW3Qfiet</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>77</v>
+      </c>
+      <c r="L20" t="n">
+        <v>771</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>lnhZhVPh</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45571.54166666666</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
         <is>
           <t>Brianteo
  (Monza)</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E21" t="n">
         <v>17102</v>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
         <is>
           <t>4YSMlwj7</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Monza</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Inter</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>77</v>
-      </c>
-      <c r="L6" t="n">
-        <v>771</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>WIJkQBF8</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45551.5625</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Abisso R.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Stadio Ennio Tardini
- (Parma)</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>27906</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>6DxlaxHN</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>rXw8YKDE</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Udinese</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>77</v>
-      </c>
-      <c r="L7" t="n">
-        <v>771</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>rgFQPs4S</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45551.65625</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Zufferli L.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Stadio Olimpico
- (Rome)</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>70634</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>URcSl02h</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Lazio</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>rJVAIaHo</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Verona</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>77</v>
-      </c>
-      <c r="L8" t="n">
-        <v>771</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>77</v>
+      </c>
+      <c r="L21" t="n">
+        <v>771</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>SIOithtm</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45571.65625</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>43147</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>77</v>
+      </c>
+      <c r="L22" t="n">
+        <v>771</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
         <is>
           <t>Serie A</t>
         </is>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,46 +512,46 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OAeKROjD</t>
+          <t>CCDxBZAc</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45558.65625</v>
+        <v>45562.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tremolada P.
+          <t>Zufferli L.
  (Ita)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Gewiss Stadium
- (Bergamo)</t>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>24950</v>
+        <v>80018</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,41 +580,46 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CCDxBZAc</t>
+          <t>pIgDNCf3</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45562.65625</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>45563.41666666666</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Sacchi J. L.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stadio Giuseppe Meazza (San Siro)
- (Milan)</t>
+          <t>Bluenergy Stadium - Stadio Friuli
+ (Udine)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>80018</v>
+        <v>25144</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -643,41 +648,46 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>pIgDNCf3</t>
+          <t>KIQjmWIj</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45563.41666666666</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>45563.54166666666</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Colombo A.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bluenergy Stadium - Stadio Friuli
- (Udine)</t>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>25144</v>
+        <v>36599</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -706,41 +716,46 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>KIQjmWIj</t>
+          <t>Whh3dzd4</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45563.54166666666</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>45563.65625</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Rapuano A.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stadio Luigi Ferraris
- (Genoa)</t>
+          <t>Stadio Renato Dall'Ara
+ (Bologna)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>36599</v>
+        <v>38279</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -769,41 +784,46 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Whh3dzd4</t>
+          <t>WxCQa92d</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45563.65625</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>45564.3125</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Sozza S.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stadio Renato Dall'Ara
- (Bologna)</t>
+          <t>Stadio Olimpico di Torino
+ (Turin)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>38279</v>
+        <v>28177</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>MZFZnvX4</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -832,41 +852,46 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>WxCQa92d</t>
+          <t>OC8I1VXq</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45564.3125</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Abisso R.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Stadio Olimpico di Torino
- (Turin)</t>
+          <t>Stadio Olimpico
+ (Rome)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>28177</v>
+        <v>70634</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>AS Roma</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -895,41 +920,46 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>OC8I1VXq</t>
+          <t>h8tCfEQG</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>45564.41666666666</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Giua A.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stadio Olimpico
- (Rome)</t>
+          <t>Stadio Giuseppe Sinigaglia
+ (Como)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>70634</v>
+        <v>13602</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>AS Roma</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -958,41 +988,46 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>h8tCfEQG</t>
+          <t>0YqKhheT</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45564.41666666666</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>45564.54166666666</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Aureliano G.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stadio Giuseppe Sinigaglia
- (Como)</t>
+          <t>Stadio Carlo Castellani
+ (Empoli)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>13602</v>
+        <v>16284</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1021,41 +1056,46 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>0YqKhheT</t>
+          <t>WETw9DuA</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45564.54166666666</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
+        <v>45564.65625</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Manganiello G.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Stadio Carlo Castellani
- (Empoli)</t>
+          <t>Stadio Diego Armando Maradona
+ (Naples)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>16284</v>
+        <v>54726</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1076,762 +1116,6 @@
         </is>
       </c>
       <c r="P10" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>WETw9DuA</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45564.65625</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Stadio Diego Armando Maradona
- (Naples)</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>54726</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Napoli</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4YSMlwj7</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Monza</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>77</v>
-      </c>
-      <c r="L11" t="n">
-        <v>771</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>vuXo7iAM</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45565.65625</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Stadio Ennio Tardini
- (Parma)</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>27906</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>6DxlaxHN</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>SCGVmKHb</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>77</v>
-      </c>
-      <c r="L12" t="n">
-        <v>771</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>z3jsi9f5</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45569.5625</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Stadio Diego Armando Maradona
- (Naples)</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>54726</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Napoli</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Como</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>77</v>
-      </c>
-      <c r="L13" t="n">
-        <v>771</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>8SWavWAa</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45569.65625</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Stadio Marc'Antonio Bentegodi
- (Verona)</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>39211</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>rJVAIaHo</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Verona</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>MkPmVv50</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Venezia</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>77</v>
-      </c>
-      <c r="L14" t="n">
-        <v>771</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>WUqjkmPH</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45570.41666666666</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Bluenergy Stadium - Stadio Friuli
- (Udine)</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>25144</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>rXw8YKDE</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Udinese</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>G8lYsMgU</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Lecce</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>77</v>
-      </c>
-      <c r="L15" t="n">
-        <v>771</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>EB8yv2aJ</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45570.54166666666</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Gewiss Stadium
- (Bergamo)</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>24950</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>8C9JjMXu</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Atalanta</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>d0PJxeie</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Genoa</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>77</v>
-      </c>
-      <c r="L16" t="n">
-        <v>771</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>ttV7xAuC</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45570.65625</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Stadio Giuseppe Meazza (San Siro)
- (Milan)</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>80018</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Inter</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>MZFZnvX4</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Torino</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>77</v>
-      </c>
-      <c r="L17" t="n">
-        <v>771</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>x8OGzlAO</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45571.3125</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Allianz Stadium
- (Turin)</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>41507</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Juventus</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>SCGVmKHb</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>77</v>
-      </c>
-      <c r="L18" t="n">
-        <v>771</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>dzYLoEIP</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45571.41666666666</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Stadio Renato Dall'Ara
- (Bologna)</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>38279</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0M9xNN8N</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Bologna</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>6DxlaxHN</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>77</v>
-      </c>
-      <c r="L19" t="n">
-        <v>771</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>SW3Qfiet</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45571.41666666666</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Stadio Olimpico
- (Rome)</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>70634</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>URcSl02h</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Lazio</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>0ESCnI1H</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Empoli</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>77</v>
-      </c>
-      <c r="L20" t="n">
-        <v>771</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>lnhZhVPh</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45571.54166666666</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Brianteo
- (Monza)</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>17102</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>4YSMlwj7</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Monza</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>zVqqL0ma</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>AS Roma</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>77</v>
-      </c>
-      <c r="L21" t="n">
-        <v>771</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>SIOithtm</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>45571.65625</v>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Stadio Artemio Franchi
- (Florence)</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>43147</v>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Fiorentina</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>8Sa8HInO</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>AC Milan</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>77</v>
-      </c>
-      <c r="L22" t="n">
-        <v>771</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
         <is>
           <t>Serie A</t>
         </is>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,46 +512,46 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CCDxBZAc</t>
+          <t>WxCQa92d</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45562.65625</v>
+        <v>45564.3125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Zufferli L.
+          <t>Sozza S.
  (Ita)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stadio Giuseppe Meazza (San Siro)
- (Milan)</t>
+          <t>Stadio Olimpico di Torino
+ (Turin)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>80018</v>
+        <v>28177</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>MZFZnvX4</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,46 +580,46 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pIgDNCf3</t>
+          <t>OC8I1VXq</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45563.41666666666</v>
+        <v>45564.41666666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sacchi J. L.
+          <t>Abisso R.
  (Ita)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bluenergy Stadium - Stadio Friuli
- (Udine)</t>
+          <t>Stadio Olimpico
+ (Rome)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>25144</v>
+        <v>70634</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>AS Roma</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -648,46 +648,46 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KIQjmWIj</t>
+          <t>h8tCfEQG</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45563.54166666666</v>
+        <v>45564.41666666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Colombo A.
+          <t>Giua A.
  (Ita)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stadio Luigi Ferraris
- (Genoa)</t>
+          <t>Stadio Giuseppe Sinigaglia
+ (Como)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>36599</v>
+        <v>13602</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -716,46 +716,46 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Whh3dzd4</t>
+          <t>0YqKhheT</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45563.65625</v>
+        <v>45564.54166666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Rapuano A.
+          <t>Aureliano G.
  (Ita)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stadio Renato Dall'Ara
- (Bologna)</t>
+          <t>Stadio Carlo Castellani
+ (Empoli)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>38279</v>
+        <v>16284</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -784,46 +784,46 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WxCQa92d</t>
+          <t>WETw9DuA</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45564.3125</v>
+        <v>45564.65625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sozza S.
+          <t>Manganiello G.
  (Ita)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stadio Olimpico di Torino
- (Turin)</t>
+          <t>Stadio Diego Armando Maradona
+ (Naples)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>28177</v>
+        <v>54726</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -852,46 +852,46 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>OC8I1VXq</t>
+          <t>vuXo7iAM</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45564.41666666666</v>
+        <v>45565.65625</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Abisso R.
+          <t>Fourneau F.
  (Ita)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Stadio Olimpico
- (Rome)</t>
+          <t>Stadio Ennio Tardini
+ (Parma)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>70634</v>
+        <v>27906</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>AS Roma</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -912,210 +912,6 @@
         </is>
       </c>
       <c r="P7" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>h8tCfEQG</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45564.41666666666</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Giua A.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Stadio Giuseppe Sinigaglia
- (Como)</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>13602</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Como</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>rJVAIaHo</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Verona</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>77</v>
-      </c>
-      <c r="L8" t="n">
-        <v>771</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>0YqKhheT</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45564.54166666666</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Aureliano G.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Stadio Carlo Castellani
- (Empoli)</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>16284</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0ESCnI1H</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Empoli</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Fiorentina</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>77</v>
-      </c>
-      <c r="L9" t="n">
-        <v>771</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>WETw9DuA</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45564.65625</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Manganiello G.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Stadio Diego Armando Maradona
- (Naples)</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>54726</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Napoli</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4YSMlwj7</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Monza</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>77</v>
-      </c>
-      <c r="L10" t="n">
-        <v>771</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
         <is>
           <t>Serie A</t>
         </is>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,46 +512,46 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>WxCQa92d</t>
+          <t>z3jsi9f5</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45564.3125</v>
+        <v>45569.5625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sozza S.
+          <t>Feliciani E.
  (Ita)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stadio Olimpico di Torino
- (Turin)</t>
+          <t>Stadio Diego Armando Maradona
+ (Naples)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>28177</v>
+        <v>54726</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,36 +580,36 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>OC8I1VXq</t>
+          <t>8SWavWAa</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45564.41666666666</v>
+        <v>45569.65625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Abisso R.
+          <t>Guida M.
  (Ita)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stadio Olimpico
- (Rome)</t>
+          <t>Stadio Marc'Antonio Bentegodi
+ (Verona)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>70634</v>
+        <v>39211</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>AS Roma</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -648,46 +648,46 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>h8tCfEQG</t>
+          <t>WUqjkmPH</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45564.41666666666</v>
+        <v>45570.41666666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Giua A.
+          <t>Mariani M.
  (Ita)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stadio Giuseppe Sinigaglia
- (Como)</t>
+          <t>Bluenergy Stadium - Stadio Friuli
+ (Udine)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>13602</v>
+        <v>25144</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -716,46 +716,46 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>0YqKhheT</t>
+          <t>EB8yv2aJ</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45564.54166666666</v>
+        <v>45570.54166666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aureliano G.
+          <t>Chiffi D.
  (Ita)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stadio Carlo Castellani
- (Empoli)</t>
+          <t>Gewiss Stadium
+ (Bergamo)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>16284</v>
+        <v>24950</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -784,46 +784,46 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WETw9DuA</t>
+          <t>ttV7xAuC</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45564.65625</v>
+        <v>45570.65625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Manganiello G.
+          <t>Marcenaro M.
  (Ita)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stadio Diego Armando Maradona
- (Naples)</t>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>54726</v>
+        <v>80018</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>MZFZnvX4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -852,36 +852,36 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vuXo7iAM</t>
+          <t>x8OGzlAO</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45565.65625</v>
+        <v>45571.3125</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fourneau F.
+          <t>Marinelli L.
  (Ita)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Stadio Ennio Tardini
- (Parma)</t>
+          <t>Allianz Stadium
+ (Turin)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>27906</v>
+        <v>41507</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -912,6 +912,404 @@
         </is>
       </c>
       <c r="P7" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>dzYLoEIP</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Di Bello M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Stadio Renato Dall'Ara
+ (Bologna)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>38279</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>77</v>
+      </c>
+      <c r="L8" t="n">
+        <v>771</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>SW3Qfiet</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ayroldi G.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>77</v>
+      </c>
+      <c r="L9" t="n">
+        <v>771</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>lnhZhVPh</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45571.54166666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>La Penna F.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Brianteo
+ (Monza)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>17102</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>77</v>
+      </c>
+      <c r="L10" t="n">
+        <v>771</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>SIOithtm</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45571.65625</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Pairetto L.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>43147</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>77</v>
+      </c>
+      <c r="L11" t="n">
+        <v>771</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Cl5M5C3L</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45584.41666666666</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Sinigaglia
+ (Como)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>13602</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>77</v>
+      </c>
+      <c r="L12" t="n">
+        <v>771</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>EXLhbUee</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45584.41666666666</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>77</v>
+      </c>
+      <c r="L13" t="n">
+        <v>771</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>Serie A</t>
         </is>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,46 +512,46 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z3jsi9f5</t>
+          <t>x8OGzlAO</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45569.5625</v>
+        <v>45571.3125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Feliciani E.
+          <t>Marinelli L.
  (Ita)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stadio Diego Armando Maradona
- (Naples)</t>
+          <t>Allianz Stadium
+ (Turin)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>54726</v>
+        <v>41507</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,46 +580,46 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8SWavWAa</t>
+          <t>dzYLoEIP</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45569.65625</v>
+        <v>45571.41666666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Guida M.
+          <t>Di Bello M.
  (Ita)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stadio Marc'Antonio Bentegodi
- (Verona)</t>
+          <t>Stadio Renato Dall'Ara
+ (Bologna)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>39211</v>
+        <v>38279</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -648,46 +648,46 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>WUqjkmPH</t>
+          <t>SW3Qfiet</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45570.41666666666</v>
+        <v>45571.41666666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mariani M.
+          <t>Ayroldi G.
  (Ita)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bluenergy Stadium - Stadio Friuli
- (Udine)</t>
+          <t>Stadio Olimpico
+ (Rome)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>25144</v>
+        <v>70634</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -716,46 +716,46 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>EB8yv2aJ</t>
+          <t>lnhZhVPh</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45570.54166666666</v>
+        <v>45571.54166666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chiffi D.
+          <t>La Penna F.
  (Ita)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Gewiss Stadium
- (Bergamo)</t>
+          <t>Brianteo
+ (Monza)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>24950</v>
+        <v>17102</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>AS Roma</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -784,46 +784,46 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ttV7xAuC</t>
+          <t>SIOithtm</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45570.65625</v>
+        <v>45571.65625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Marcenaro M.
+          <t>Pairetto L.
  (Ita)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stadio Giuseppe Meazza (San Siro)
- (Milan)</t>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>80018</v>
+        <v>43147</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -852,46 +852,41 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>x8OGzlAO</t>
+          <t>Cl5M5C3L</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45571.3125</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Marinelli L.
- (Ita)</t>
-        </is>
-      </c>
+        <v>45584.41666666666</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Allianz Stadium
- (Turin)</t>
+          <t>Stadio Giuseppe Sinigaglia
+ (Como)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>41507</v>
+        <v>13602</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -920,46 +915,41 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>dzYLoEIP</t>
+          <t>EXLhbUee</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45571.41666666666</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Di Bello M.
- (Ita)</t>
-        </is>
-      </c>
+        <v>45584.41666666666</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stadio Renato Dall'Ara
- (Bologna)</t>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>38279</v>
+        <v>36599</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>0M9xNN8N</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Bologna</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>6DxlaxHN</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Parma</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -988,46 +978,41 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SW3Qfiet</t>
+          <t>SznSCTAl</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45571.41666666666</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ayroldi G.
- (Ita)</t>
-        </is>
-      </c>
+        <v>45584.54166666666</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stadio Olimpico
- (Rome)</t>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>70634</v>
+        <v>80018</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1056,46 +1041,41 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>lnhZhVPh</t>
+          <t>2g2mKBIE</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45571.54166666666</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>La Penna F.
- (Ita)</t>
-        </is>
-      </c>
+        <v>45584.65625</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Brianteo
- (Monza)</t>
+          <t>Allianz Stadium
+ (Turin)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>17102</v>
+        <v>41507</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>AS Roma</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1124,46 +1104,41 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>SIOithtm</t>
+          <t>8Kjh0jRr</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45571.65625</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Pairetto L.
- (Ita)</t>
-        </is>
-      </c>
+        <v>45585.3125</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Stadio Artemio Franchi
- (Florence)</t>
+          <t>Stadio Carlo Castellani
+ (Empoli)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>43147</v>
+        <v>16284</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1192,41 +1167,41 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cl5M5C3L</t>
+          <t>AJ5eIkmR</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45584.41666666666</v>
+        <v>45585.41666666666</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Stadio Giuseppe Sinigaglia
- (Como)</t>
+          <t>Stadio Via del Mare
+ (Lecce)</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>13602</v>
+        <v>40670</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1255,41 +1230,41 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>EXLhbUee</t>
+          <t>dGwq9oAD</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45584.41666666666</v>
+        <v>45585.41666666666</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Stadio Luigi Ferraris
- (Genoa)</t>
+          <t>Stadio Pierluigi Penzo
+ (Venice)</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>36599</v>
+        <v>11150</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1310,6 +1285,132 @@
         </is>
       </c>
       <c r="P13" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>GMBD7YY8</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45585.54166666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Unipol Domus
+ (Cagliari)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>16416</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>77</v>
+      </c>
+      <c r="L14" t="n">
+        <v>771</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>0lpzB7u1</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45585.65625</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>77</v>
+      </c>
+      <c r="L15" t="n">
+        <v>771</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>Serie A</t>
         </is>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,7 +518,12 @@
       <c r="B2" s="2" t="n">
         <v>45584.41666666666</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Fabbri M.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Stadio Giuseppe Sinigaglia
@@ -581,7 +586,12 @@
       <c r="B3" s="2" t="n">
         <v>45584.41666666666</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Doveri D.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>Stadio Luigi Ferraris
@@ -644,7 +654,12 @@
       <c r="B4" s="2" t="n">
         <v>45584.54166666666</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Chiffi D.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>Stadio Giuseppe Meazza (San Siro)
@@ -707,7 +722,12 @@
       <c r="B5" s="2" t="n">
         <v>45584.65625</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Sacchi J. L.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Allianz Stadium
@@ -770,7 +790,12 @@
       <c r="B6" s="2" t="n">
         <v>45585.3125</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Abisso R.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>Stadio Carlo Castellani
@@ -833,7 +858,12 @@
       <c r="B7" s="2" t="n">
         <v>45585.41666666666</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Fourneau F.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Stadio Via del Mare
@@ -896,7 +926,12 @@
       <c r="B8" s="2" t="n">
         <v>45585.41666666666</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Zufferli L.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>Stadio Pierluigi Penzo
@@ -959,7 +994,12 @@
       <c r="B9" s="2" t="n">
         <v>45585.54166666666</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Aureliano G.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>Unipol Domus
@@ -1022,7 +1062,12 @@
       <c r="B10" s="2" t="n">
         <v>45585.65625</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Massa D.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>Stadio Olimpico
@@ -1085,7 +1130,12 @@
       <c r="B11" s="2" t="n">
         <v>45586.65625</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Dionisi F.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>Stadio Marc'Antonio Bentegodi
@@ -1953,6 +2003,321 @@
         </is>
       </c>
       <c r="P24" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>IFm4IHT9</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45595.60416666666</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Stadio Carlo Castellani
+ (Empoli)</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>16284</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>77</v>
+      </c>
+      <c r="L25" t="n">
+        <v>771</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>0b5fTYsS</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45595.60416666666</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Stadio Pierluigi Penzo
+ (Venice)</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>11150</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>77</v>
+      </c>
+      <c r="L26" t="n">
+        <v>771</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Y96v2dqT</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45595.69791666666</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Gewiss Stadium
+ (Bergamo)</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>24950</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>77</v>
+      </c>
+      <c r="L27" t="n">
+        <v>771</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>rcXrBZLq</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45595.69791666666</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Allianz Stadium
+ (Turin)</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>41507</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>77</v>
+      </c>
+      <c r="L28" t="n">
+        <v>771</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>EssDGebM</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45596.60416666666</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>77</v>
+      </c>
+      <c r="L29" t="n">
+        <v>771</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
         <is>
           <t>Serie A</t>
         </is>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2323,6 +2323,132 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Sp7nVfDF</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45596.69791666666</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>77</v>
+      </c>
+      <c r="L30" t="n">
+        <v>771</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>p2kdKwac</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45596.69791666666</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Sinigaglia
+ (Como)</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>13602</v>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>77</v>
+      </c>
+      <c r="L31" t="n">
+        <v>771</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,406 +512,1888 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8Kjh0jRr</t>
+          <t>I5fXHFho</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45585.3125</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Abisso R.
- (Ita)</t>
-        </is>
-      </c>
+        <v>45590.5625</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>Bluenergy Stadium - Stadio Friuli
+ (Udine)</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>25144</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>77</v>
+      </c>
+      <c r="L2" t="n">
+        <v>771</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>bLD0NyVN</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45590.65625</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico di Torino
+ (Turin)</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>28177</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>77</v>
+      </c>
+      <c r="L3" t="n">
+        <v>771</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>UuMqRJVb</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45591.41666666666</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Stadio Diego Armando Maradona
+ (Naples)</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>54726</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>77</v>
+      </c>
+      <c r="L4" t="n">
+        <v>771</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>8f71RSPs</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45591.54166666666</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Stadio Renato Dall'Ara
+ (Bologna)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>38279</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>77</v>
+      </c>
+      <c r="L5" t="n">
+        <v>771</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>OMVUWl2K</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45591.65625</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Gewiss Stadium
+ (Bergamo)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>24950</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>77</v>
+      </c>
+      <c r="L6" t="n">
+        <v>771</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>jeAhPc0B</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45592.35416666666</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Stadio Ennio Tardini
+ (Parma)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>27906</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>77</v>
+      </c>
+      <c r="L7" t="n">
+        <v>771</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>OjcQLOgJ</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>77</v>
+      </c>
+      <c r="L8" t="n">
+        <v>771</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>xY3xTu1n</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Brianteo
+ (Monza)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>17102</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>77</v>
+      </c>
+      <c r="L9" t="n">
+        <v>771</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>jwaINpP6</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45592.58333333334</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>77</v>
+      </c>
+      <c r="L10" t="n">
+        <v>771</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>fB59P6ff</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45592.69791666666</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>43147</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>77</v>
+      </c>
+      <c r="L11" t="n">
+        <v>771</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Ug79dz7j</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45594.60416666666</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Unipol Domus
+ (Cagliari)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>16416</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>77</v>
+      </c>
+      <c r="L12" t="n">
+        <v>771</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>4CLi9Djd</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45594.60416666666</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Stadio Via del Mare
+ (Lecce)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>40670</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>77</v>
+      </c>
+      <c r="L13" t="n">
+        <v>771</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>WIDwXGr3</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45594.69791666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>77</v>
+      </c>
+      <c r="L14" t="n">
+        <v>771</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IFm4IHT9</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45595.60416666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
         <is>
           <t>Stadio Carlo Castellani
  (Empoli)</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E15" t="n">
         <v>16284</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
         <is>
           <t>0ESCnI1H</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Empoli</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Napoli</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>77</v>
-      </c>
-      <c r="L2" t="n">
-        <v>771</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>AJ5eIkmR</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>45585.41666666666</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Fourneau F.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Stadio Via del Mare
- (Lecce)</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>40670</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>G8lYsMgU</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Lecce</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Fiorentina</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>77</v>
-      </c>
-      <c r="L3" t="n">
-        <v>771</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>dGwq9oAD</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45585.41666666666</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Zufferli L.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>77</v>
+      </c>
+      <c r="L15" t="n">
+        <v>771</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>0b5fTYsS</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45595.60416666666</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Stadio Pierluigi Penzo
  (Venice)</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E16" t="n">
         <v>11150</v>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
         <is>
           <t>MkPmVv50</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Venezia</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>77</v>
+      </c>
+      <c r="L16" t="n">
+        <v>771</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Y96v2dqT</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45595.69791666666</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Gewiss Stadium
+ (Bergamo)</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>24950</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
         <is>
           <t>8C9JjMXu</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Atalanta</t>
         </is>
       </c>
-      <c r="K4" t="n">
-        <v>77</v>
-      </c>
-      <c r="L4" t="n">
-        <v>771</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>GMBD7YY8</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45585.54166666666</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Aureliano G.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Unipol Domus
- (Cagliari)</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>16416</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SCGVmKHb</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>MZFZnvX4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Torino</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>77</v>
-      </c>
-      <c r="L5" t="n">
-        <v>771</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>0lpzB7u1</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45585.65625</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Massa D.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>77</v>
+      </c>
+      <c r="L17" t="n">
+        <v>771</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>rcXrBZLq</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45595.69791666666</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Allianz Stadium
+ (Turin)</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>41507</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>77</v>
+      </c>
+      <c r="L18" t="n">
+        <v>771</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>EssDGebM</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45596.60416666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>77</v>
+      </c>
+      <c r="L19" t="n">
+        <v>771</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Sp7nVfDF</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45596.69791666666</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
         <is>
           <t>Stadio Olimpico
  (Rome)</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E20" t="n">
         <v>70634</v>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
         <is>
           <t>zVqqL0ma</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>AS Roma</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Inter</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>77</v>
-      </c>
-      <c r="L6" t="n">
-        <v>771</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>McP0d8Q7</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45586.65625</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Dionisi F.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>77</v>
+      </c>
+      <c r="L20" t="n">
+        <v>771</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>p2kdKwac</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45596.69791666666</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Sinigaglia
+ (Como)</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>13602</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>77</v>
+      </c>
+      <c r="L21" t="n">
+        <v>771</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>rJ8JNC5k</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45598.45833333334</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Stadio Renato Dall'Ara
+ (Bologna)</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>38279</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>77</v>
+      </c>
+      <c r="L22" t="n">
+        <v>771</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>pOryx3Qa</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45598.58333333334</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Bluenergy Stadium - Stadio Friuli
+ (Udine)</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>25144</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>77</v>
+      </c>
+      <c r="L23" t="n">
+        <v>771</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Gpn0zjke</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45598.69791666666</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Brianteo
+ (Monza)</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>17102</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>77</v>
+      </c>
+      <c r="L24" t="n">
+        <v>771</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>CCu9YTJ7</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45599.35416666666</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Stadio Diego Armando Maradona
+ (Naples)</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>54726</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>77</v>
+      </c>
+      <c r="L25" t="n">
+        <v>771</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>b7pTwPem</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45599.45833333334</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico di Torino
+ (Turin)</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>28177</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>77</v>
+      </c>
+      <c r="L26" t="n">
+        <v>771</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>WvkEqfS8</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45599.58333333334</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
         <is>
           <t>Stadio Marc'Antonio Bentegodi
  (Verona)</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E27" t="n">
         <v>39211</v>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
         <is>
           <t>rJVAIaHo</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Verona</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4YSMlwj7</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Monza</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>77</v>
-      </c>
-      <c r="L7" t="n">
-        <v>771</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>77</v>
+      </c>
+      <c r="L27" t="n">
+        <v>771</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>v5hMsYdL</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45599.69791666666</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>77</v>
+      </c>
+      <c r="L28" t="n">
+        <v>771</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>jqCRLjz2</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45600.60416666666</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Stadio Carlo Castellani
+ (Empoli)</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>16284</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>77</v>
+      </c>
+      <c r="L29" t="n">
+        <v>771</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>vJXfdXBE</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45600.60416666666</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Stadio Ennio Tardini
+ (Parma)</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>27906</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>77</v>
+      </c>
+      <c r="L30" t="n">
+        <v>771</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>rXmhxCKr</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45600.69791666666</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>77</v>
+      </c>
+      <c r="L31" t="n">
+        <v>771</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
         <is>
           <t>Serie A</t>
         </is>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,610 +512,1938 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>I5fXHFho</t>
+          <t>Ug79dz7j</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45590.5625</v>
+        <v>45594.60416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Manganiello G.
+          <t>Fourneau F.
  (Ita)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>Unipol Domus
+ (Cagliari)</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>16416</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>77</v>
+      </c>
+      <c r="L2" t="n">
+        <v>771</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>4CLi9Djd</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45594.60416666666</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Mariani M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Stadio Via del Mare
+ (Lecce)</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>40670</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>77</v>
+      </c>
+      <c r="L3" t="n">
+        <v>771</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>WIDwXGr3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45594.69791666666</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Colombo A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>77</v>
+      </c>
+      <c r="L4" t="n">
+        <v>771</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>IFm4IHT9</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45595.60416666666</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Marchetti M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Stadio Carlo Castellani
+ (Empoli)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>16284</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>77</v>
+      </c>
+      <c r="L5" t="n">
+        <v>771</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>0b5fTYsS</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45595.60416666666</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Massa D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Stadio Pierluigi Penzo
+ (Venice)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>11150</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>77</v>
+      </c>
+      <c r="L6" t="n">
+        <v>771</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Y96v2dqT</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45595.69791666666</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Piccinini M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Gewiss Stadium
+ (Bergamo)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>24950</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>77</v>
+      </c>
+      <c r="L7" t="n">
+        <v>771</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>rcXrBZLq</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45595.69791666666</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Zufferli L.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Allianz Stadium
+ (Turin)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>41507</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>77</v>
+      </c>
+      <c r="L8" t="n">
+        <v>771</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>EssDGebM</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45596.60416666666</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Chiffi D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>77</v>
+      </c>
+      <c r="L9" t="n">
+        <v>771</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Sp7nVfDF</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45596.69791666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Fabbri M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>77</v>
+      </c>
+      <c r="L10" t="n">
+        <v>771</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>p2kdKwac</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45596.69791666666</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Pairetto L.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Sinigaglia
+ (Como)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>13602</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>77</v>
+      </c>
+      <c r="L11" t="n">
+        <v>771</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>rJ8JNC5k</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45598.45833333334</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Stadio Renato Dall'Ara
+ (Bologna)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>38279</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>77</v>
+      </c>
+      <c r="L12" t="n">
+        <v>771</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>pOryx3Qa</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45598.58333333334</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Bluenergy Stadium - Stadio Friuli
  (Udine)</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E13" t="n">
         <v>25144</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
         <is>
           <t>rXw8YKDE</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Udinese</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>SCGVmKHb</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>77</v>
-      </c>
-      <c r="L2" t="n">
-        <v>771</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>bLD0NyVN</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>45590.65625</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ayroldi G.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>77</v>
+      </c>
+      <c r="L13" t="n">
+        <v>771</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Gpn0zjke</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45598.69791666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Brianteo
+ (Monza)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>17102</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>77</v>
+      </c>
+      <c r="L14" t="n">
+        <v>771</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>CCu9YTJ7</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45599.35416666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Stadio Diego Armando Maradona
+ (Naples)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>54726</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>77</v>
+      </c>
+      <c r="L15" t="n">
+        <v>771</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>b7pTwPem</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45599.45833333334</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Stadio Olimpico di Torino
  (Turin)</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E16" t="n">
         <v>28177</v>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
         <is>
           <t>MZFZnvX4</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Torino</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>77</v>
+      </c>
+      <c r="L16" t="n">
+        <v>771</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>WvkEqfS8</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45599.58333333334</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Stadio Marc'Antonio Bentegodi
+ (Verona)</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>39211</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>77</v>
+      </c>
+      <c r="L17" t="n">
+        <v>771</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>v5hMsYdL</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45599.69791666666</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>77</v>
+      </c>
+      <c r="L18" t="n">
+        <v>771</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>jqCRLjz2</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45600.60416666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Stadio Carlo Castellani
+ (Empoli)</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>16284</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>ttyLthOA</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="K3" t="n">
-        <v>77</v>
-      </c>
-      <c r="L3" t="n">
-        <v>771</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>UuMqRJVb</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45591.41666666666</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Tremolada P.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Stadio Diego Armando Maradona
- (Naples)</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>54726</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Napoli</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="K19" t="n">
+        <v>77</v>
+      </c>
+      <c r="L19" t="n">
+        <v>771</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>vJXfdXBE</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45600.60416666666</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Stadio Ennio Tardini
+ (Parma)</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>27906</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>77</v>
+      </c>
+      <c r="L20" t="n">
+        <v>771</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>rXmhxCKr</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45600.69791666666</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>77</v>
+      </c>
+      <c r="L21" t="n">
+        <v>771</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>bR8Aj2ug</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45603.69791666666</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>77</v>
+      </c>
+      <c r="L22" t="n">
+        <v>771</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>OYgzob9U</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45604.69791666666</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Stadio Via del Mare
+ (Lecce)</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>40670</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
         <is>
           <t>G8lYsMgU</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Lecce</t>
         </is>
       </c>
-      <c r="K4" t="n">
-        <v>77</v>
-      </c>
-      <c r="L4" t="n">
-        <v>771</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>OMVUWl2K</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45591.65625</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Feliciani E.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>77</v>
+      </c>
+      <c r="L23" t="n">
+        <v>771</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>hO2h1JgB</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45605.45833333334</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Stadio Pierluigi Penzo
+ (Venice)</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>11150</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>77</v>
+      </c>
+      <c r="L24" t="n">
+        <v>771</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>E3zhYKPO</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45605.58333333334</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Unipol Domus
+ (Cagliari)</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>16416</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>77</v>
+      </c>
+      <c r="L25" t="n">
+        <v>771</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>S60RnKvI</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45605.69791666666</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Allianz Stadium
+ (Turin)</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>41507</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>77</v>
+      </c>
+      <c r="L26" t="n">
+        <v>771</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>tjxpzseC</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45606.35416666666</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
         <is>
           <t>Gewiss Stadium
  (Bergamo)</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E27" t="n">
         <v>24950</v>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
         <is>
           <t>8C9JjMXu</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Atalanta</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>rJVAIaHo</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Verona</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>77</v>
-      </c>
-      <c r="L5" t="n">
-        <v>771</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>jeAhPc0B</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45592.35416666666</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>La Penna F.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Stadio Ennio Tardini
- (Parma)</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>27906</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>6DxlaxHN</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0ESCnI1H</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Empoli</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>77</v>
-      </c>
-      <c r="L6" t="n">
-        <v>771</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>OjcQLOgJ</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45592.45833333334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Piccinini M.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>77</v>
+      </c>
+      <c r="L27" t="n">
+        <v>771</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>pbap3uPb</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45606.45833333334</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
         <is>
           <t>Stadio Olimpico
  (Rome)</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E28" t="n">
         <v>70634</v>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>URcSl02h</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Lazio</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>d0PJxeie</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Genoa</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>77</v>
-      </c>
-      <c r="L7" t="n">
-        <v>771</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>xY3xTu1n</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45592.45833333334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Rapuano A.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>77</v>
+      </c>
+      <c r="L28" t="n">
+        <v>771</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>hU52hOAt</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45606.45833333334</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>43147</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>77</v>
+      </c>
+      <c r="L29" t="n">
+        <v>771</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>voUq51fn</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45606.58333333334</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
         <is>
           <t>Brianteo
  (Monza)</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E30" t="n">
         <v>17102</v>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
         <is>
           <t>4YSMlwj7</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Monza</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>MkPmVv50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Venezia</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>77</v>
-      </c>
-      <c r="L8" t="n">
-        <v>771</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>jwaINpP6</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45592.58333333334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Guida M.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>77</v>
+      </c>
+      <c r="L30" t="n">
+        <v>771</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>KtcJltA5</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45606.69791666666</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
         <is>
           <t>Stadio Giuseppe Meazza (San Siro)
  (Milan)</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E31" t="n">
         <v>80018</v>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
         <is>
           <t>Iw7eKK25</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Inter</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Juventus</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>77</v>
-      </c>
-      <c r="L9" t="n">
-        <v>771</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>fB59P6ff</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45592.69791666666</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Sozza S.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Stadio Artemio Franchi
- (Florence)</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>43147</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Fiorentina</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>zVqqL0ma</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>AS Roma</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>77</v>
-      </c>
-      <c r="L10" t="n">
-        <v>771</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>77</v>
+      </c>
+      <c r="L31" t="n">
+        <v>771</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
         <is>
           <t>Serie A</t>
         </is>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -512,41 +512,41 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>rJ8JNC5k</t>
+          <t>bR8Aj2ug</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45598.45833333334</v>
+        <v>45603.69791666666</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stadio Renato Dall'Ara
- (Bologna)</t>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>38279</v>
+        <v>36599</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -575,41 +575,41 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pOryx3Qa</t>
+          <t>OYgzob9U</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45598.58333333334</v>
+        <v>45604.69791666666</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bluenergy Stadium - Stadio Friuli
- (Udine)</t>
+          <t>Stadio Via del Mare
+ (Lecce)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>25144</v>
+        <v>40670</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -638,41 +638,41 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Gpn0zjke</t>
+          <t>hO2h1JgB</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45598.69791666666</v>
+        <v>45605.45833333334</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Brianteo
- (Monza)</t>
+          <t>Stadio Pierluigi Penzo
+ (Venice)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>17102</v>
+        <v>11150</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -701,41 +701,41 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>CCu9YTJ7</t>
+          <t>E3zhYKPO</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45599.35416666666</v>
+        <v>45605.58333333334</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stadio Diego Armando Maradona
- (Naples)</t>
+          <t>Unipol Domus
+ (Cagliari)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>54726</v>
+        <v>16416</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -764,41 +764,41 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>b7pTwPem</t>
+          <t>S60RnKvI</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45599.45833333334</v>
+        <v>45605.69791666666</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stadio Olimpico di Torino
+          <t>Allianz Stadium
  (Turin)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>28177</v>
+        <v>41507</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>MZFZnvX4</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Torino</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Fiorentina</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -827,41 +827,41 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>WvkEqfS8</t>
+          <t>tjxpzseC</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45599.58333333334</v>
+        <v>45606.35416666666</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Stadio Marc'Antonio Bentegodi
- (Verona)</t>
+          <t>Gewiss Stadium
+ (Bergamo)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>39211</v>
+        <v>24950</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>AS Roma</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -890,41 +890,41 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>v5hMsYdL</t>
+          <t>pbap3uPb</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45599.69791666666</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stadio Giuseppe Meazza (San Siro)
- (Milan)</t>
+          <t>Stadio Olimpico
+ (Rome)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>80018</v>
+        <v>70634</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>AS Roma</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -953,41 +953,41 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>jqCRLjz2</t>
+          <t>hU52hOAt</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45600.60416666666</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stadio Carlo Castellani
- (Empoli)</t>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>16284</v>
+        <v>43147</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1016,41 +1016,41 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>vJXfdXBE</t>
+          <t>voUq51fn</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45600.60416666666</v>
+        <v>45606.58333333334</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Stadio Ennio Tardini
- (Parma)</t>
+          <t>Brianteo
+ (Monza)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>27906</v>
+        <v>17102</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1079,41 +1079,41 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>rXmhxCKr</t>
+          <t>KtcJltA5</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45600.69791666666</v>
+        <v>45606.69791666666</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Stadio Olimpico
- (Rome)</t>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>70634</v>
+        <v>80018</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="K11" t="n">

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,41 +512,46 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bR8Aj2ug</t>
+          <t>OYgzob9U</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45603.69791666666</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>45604.69791666666</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Sacchi J. L.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stadio Luigi Ferraris
- (Genoa)</t>
+          <t>Stadio Via del Mare
+ (Lecce)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>36599</v>
+        <v>40670</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -575,41 +580,46 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>OYgzob9U</t>
+          <t>hO2h1JgB</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45604.69791666666</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>45605.45833333334</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Chiffi D.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stadio Via del Mare
- (Lecce)</t>
+          <t>Stadio Pierluigi Penzo
+ (Venice)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>40670</v>
+        <v>11150</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -638,41 +648,46 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hO2h1JgB</t>
+          <t>E3zhYKPO</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45605.45833333334</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>45605.58333333334</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Fabbri M.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stadio Pierluigi Penzo
- (Venice)</t>
+          <t>Unipol Domus
+ (Cagliari)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>11150</v>
+        <v>16416</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -701,41 +716,46 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>E3zhYKPO</t>
+          <t>S60RnKvI</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45605.58333333334</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>45605.69791666666</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Sozza S.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Unipol Domus
- (Cagliari)</t>
+          <t>Allianz Stadium
+ (Turin)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>16416</v>
+        <v>41507</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>MZFZnvX4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -764,41 +784,46 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>S60RnKvI</t>
+          <t>tjxpzseC</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45605.69791666666</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>45606.35416666666</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Di Bello M.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Allianz Stadium
- (Turin)</t>
+          <t>Gewiss Stadium
+ (Bergamo)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>41507</v>
+        <v>24950</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -827,41 +852,46 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tjxpzseC</t>
+          <t>pbap3uPb</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45606.35416666666</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>45606.45833333334</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Manganiello G.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Gewiss Stadium
- (Bergamo)</t>
+          <t>Stadio Olimpico
+ (Rome)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>24950</v>
+        <v>70634</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>AS Roma</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -890,41 +920,46 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>pbap3uPb</t>
+          <t>hU52hOAt</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>45606.45833333334</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Zufferli L.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stadio Olimpico
- (Rome)</t>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>70634</v>
+        <v>43147</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>AS Roma</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -953,41 +988,46 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hU52hOAt</t>
+          <t>voUq51fn</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45606.45833333334</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>45606.58333333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Colombo A.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stadio Artemio Franchi
- (Florence)</t>
+          <t>Brianteo
+ (Monza)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>43147</v>
+        <v>17102</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1016,41 +1056,46 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>voUq51fn</t>
+          <t>KtcJltA5</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45606.58333333334</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
+        <v>45606.69791666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Mariani M.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Brianteo
- (Monza)</t>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>17102</v>
+        <v>80018</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1079,61 +1124,124 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>KtcJltA5</t>
+          <t>WENRFI84</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45606.69791666666</v>
+        <v>45619.45833333334</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
+          <t>Stadio Marc'Antonio Bentegodi
+ (Verona)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>39211</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>77</v>
+      </c>
+      <c r="L11" t="n">
+        <v>771</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>z7KrCz8T</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45619.58333333334</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>Stadio Giuseppe Meazza (San Siro)
  (Milan)</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E12" t="n">
         <v>80018</v>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Inter</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Napoli</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
         <v>77</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L12" t="n">
         <v>771</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M12" t="n">
         <v>0</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N12" t="n">
         <v>20242025</v>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>Serie A</t>
         </is>
